--- a/data/trans_orig/P1432-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1432-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de incontinencia urinaria en 2007</t>
+          <t>Población con diagnóstico de incontinencia urinaria en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15415</t>
+          <t>15053</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>264102</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>249534</t>
+          <t>249818</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258994</t>
+          <t>259237</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>518433</t>
+          <t>518795</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>530568</t>
+          <t>530487</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>14943</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18822</t>
+          <t>17588</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>485932</t>
+          <t>485997</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>487404</t>
+          <t>489006</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500044</t>
+          <t>499995</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>978202</t>
+          <t>979436</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>992044</t>
+          <t>991994</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9359</t>
+          <t>9774</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12448</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15961</t>
+          <t>17294</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309487</t>
+          <t>309072</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317880</t>
+          <t>317872</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>322964</t>
+          <t>323286</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333356</t>
+          <t>333349</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>638297</t>
+          <t>636964</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>650059</t>
+          <t>649443</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11106</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>351604</t>
+          <t>351759</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357849</t>
+          <t>358671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>364292</t>
+          <t>364007</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>719021</t>
+          <t>720024</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>728317</t>
+          <t>728372</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -2104,97 +2104,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1885</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7543</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>2057</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6567</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>7391</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2057</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>7136</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201423</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>203308</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201101</t>
+          <t>200125</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>403840</t>
+          <t>403585</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6462</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>969</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9730</t>
+          <t>9048</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264349</t>
+          <t>265606</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>539225</t>
+          <t>539907</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>547979</t>
+          <t>547986</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>971</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>9594</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16889</t>
+          <t>17760</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>602573</t>
+          <t>601739</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>613171</t>
+          <t>613254</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>629257</t>
+          <t>628625</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>637271</t>
+          <t>637248</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1236357</t>
+          <t>1235486</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1249418</t>
+          <t>1248529</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>12142</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28071</t>
+          <t>27834</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13873</t>
+          <t>13613</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33425</t>
+          <t>33269</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30065</t>
+          <t>28923</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>54606</t>
+          <t>55248</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>715724</t>
+          <t>715961</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>731670</t>
+          <t>731653</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>750086</t>
+          <t>750242</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>769638</t>
+          <t>769898</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1472700</t>
+          <t>1472058</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1497241</t>
+          <t>1498383</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26042</t>
+          <t>26480</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48980</t>
+          <t>49392</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>37704</t>
+          <t>38308</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>65998</t>
+          <t>68044</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>70998</t>
+          <t>68992</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>106205</t>
+          <t>106354</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3227563</t>
+          <t>3227151</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3250501</t>
+          <t>3250063</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3313199</t>
+          <t>3311153</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3341493</t>
+          <t>3340889</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6549536</t>
+          <t>6549387</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6584743</t>
+          <t>6586749</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de incontinencia urinaria en 2012</t>
+          <t>Población con diagnóstico de incontinencia urinaria en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,47 +4090,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7853</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2960</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>932</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8899</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2960</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>8729</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>292739</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>294738</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278346</t>
+          <t>279392</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286313</t>
+          <t>286312</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573430</t>
+          <t>573254</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>581046</t>
+          <t>581051</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22826</t>
+          <t>23199</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25077</t>
+          <t>24628</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>499631</t>
+          <t>499816</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>499830</t>
+          <t>499457</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>516205</t>
+          <t>515992</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1003107</t>
+          <t>1003556</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1020644</t>
+          <t>1020335</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -4741,97 +4741,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2085</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1944</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6482</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>2085</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6934</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>7300</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2085</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>6906</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>322102</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324046</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>334086</t>
+          <t>334538</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>658160</t>
+          <t>657766</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12632</t>
+          <t>12533</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15459</t>
+          <t>15528</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>367506</t>
+          <t>367085</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>376319</t>
+          <t>376418</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386813</t>
+          <t>386717</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>747474</t>
+          <t>747405</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>758999</t>
+          <t>759006</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14744</t>
+          <t>14041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>19203</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>8389</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25698</t>
+          <t>27672</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197874</t>
+          <t>198577</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211519</t>
+          <t>211580</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201932</t>
+          <t>200388</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214403</t>
+          <t>214267</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>406511</t>
+          <t>404537</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>423902</t>
+          <t>423820</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11545</t>
+          <t>11579</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>12596</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>269182</t>
+          <t>269169</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>266551</t>
+          <t>266517</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276053</t>
+          <t>276040</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>539467</t>
+          <t>539481</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549980</t>
+          <t>549965</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>19183</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17234</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11124</t>
+          <t>11873</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31549</t>
+          <t>30842</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>642836</t>
+          <t>643605</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>657652</t>
+          <t>657666</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>676619</t>
+          <t>677551</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>689844</t>
+          <t>689944</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1325092</t>
+          <t>1325799</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1345517</t>
+          <t>1344768</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6476,42 +6476,42 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>9871</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>4391</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>18537</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
           <t>1,2%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>9871</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>5334</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>17936</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21926</t>
+          <t>21735</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>769750</t>
+          <t>769816</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>778079</t>
+          <t>778081</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,47 +6584,47 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>98,81%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>99,87%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>812707</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>804041</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>818187</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
           <t>98,8%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>99,87%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>747</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>812707</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>804642</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>817244</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>98,8%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1579750</t>
+          <t>1579941</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1595161</t>
+          <t>1595070</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14075</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37129</t>
+          <t>34740</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>44781</t>
+          <t>43029</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>74842</t>
+          <t>75272</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>62231</t>
+          <t>64090</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>100120</t>
+          <t>101372</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3389650</t>
+          <t>3392039</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3412704</t>
+          <t>3413214</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3479148</t>
+          <t>3478718</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3509209</t>
+          <t>3510961</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6880649</t>
+          <t>6879397</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6918538</t>
+          <t>6916679</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de incontinencia urinaria en 2016</t>
+          <t>Población con diagnóstico de incontinencia urinaria en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>799</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12259</t>
+          <t>11362</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16276</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285087</t>
+          <t>284985</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292970</t>
+          <t>292962</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>276444</t>
+          <t>277341</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286748</t>
+          <t>286816</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>566188</t>
+          <t>566283</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578724</t>
+          <t>578547</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7859</t>
+          <t>7090</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7741,77 +7741,77 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4737</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1164</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11204</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>7349</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>3410</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>15960</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>1,56%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4737</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1165</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11620</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>7349</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>14760</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>494716</t>
+          <t>495485</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7849,82 +7849,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>98,59%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>518347</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>511880</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>521920</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,78%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>952</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1018310</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1009699</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1022249</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>99,28%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>98,44%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>518347</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>511464</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>521919</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,78%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>952</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1018310</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1010899</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1022768</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -8064,97 +8064,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1820</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1939</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>1882</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>316745</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318565</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>334370</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>336309</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>652992</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>654874</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8007</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25578</t>
+          <t>24356</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9007</t>
+          <t>9522</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27455</t>
+          <t>26170</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>364577</t>
+          <t>365076</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>361705</t>
+          <t>362927</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>379276</t>
+          <t>379038</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>729792</t>
+          <t>731077</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>748240</t>
+          <t>747725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,62 +8785,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1873</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4776</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4966</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>206067</t>
+          <t>206405</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>216714</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>218587</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>424842</t>
+          <t>425032</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9644</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>959</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>9215</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15343</t>
+          <t>15258</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253479</t>
+          <t>253614</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261491</t>
+          <t>261512</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>263097</t>
+          <t>263900</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272157</t>
+          <t>272156</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>520895</t>
+          <t>520980</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532664</t>
+          <t>532582</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9583</t>
+          <t>9371</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25919</t>
+          <t>26552</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12482</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31175</t>
+          <t>31320</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>648377</t>
+          <t>647519</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>665375</t>
+          <t>664742</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>681711</t>
+          <t>681923</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1316677</t>
+          <t>1316532</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1335370</t>
+          <t>1335851</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14336</t>
+          <t>12749</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15893</t>
+          <t>16849</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>771004</t>
+          <t>770390</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>811831</t>
+          <t>813418</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>823880</t>
+          <t>824024</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1588857</t>
+          <t>1587901</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1601217</t>
+          <t>1601403</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26742</t>
+          <t>26279</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>37745</t>
+          <t>38462</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>65875</t>
+          <t>69353</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>52845</t>
+          <t>53794</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>88229</t>
+          <t>87626</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3367608</t>
+          <t>3368071</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3383140</t>
+          <t>3383759</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3478667</t>
+          <t>3475189</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3506797</t>
+          <t>3506080</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6850663</t>
+          <t>6851266</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6886047</t>
+          <t>6885098</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1432-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1432-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9260</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>12555</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15053</t>
+          <t>14860</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>263750</t>
+          <t>264203</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>249818</t>
+          <t>248283</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259237</t>
+          <t>258985</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>518795</t>
+          <t>518988</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>530487</t>
+          <t>530888</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14943</t>
+          <t>14693</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17588</t>
+          <t>18338</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>485997</t>
+          <t>486055</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489006</t>
+          <t>489256</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>499995</t>
+          <t>500190</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>979436</t>
+          <t>978686</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>991994</t>
+          <t>991985</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9774</t>
+          <t>9018</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>12293</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17294</t>
+          <t>16761</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309072</t>
+          <t>309828</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317872</t>
+          <t>317822</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323286</t>
+          <t>323119</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333349</t>
+          <t>333173</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>636964</t>
+          <t>637497</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>649443</t>
+          <t>650134</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -1761,62 +1761,62 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6259</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2086</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6912</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6394</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2086</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7449</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>11294</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>351759</t>
+          <t>352412</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358671</t>
+          <t>357851</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,49 +1889,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>99,77%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>369370</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>365062</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>371456</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,44%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,28%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>369370</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>364007</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>371456</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,99%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>741</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>720024</t>
+          <t>718833</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>728372</t>
+          <t>728375</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200125</t>
+          <t>200619</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>403585</t>
+          <t>403883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>6513</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>967</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9048</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265606</t>
+          <t>264298</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>271012</t>
+          <t>271038</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>539907</t>
+          <t>539891</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>547986</t>
+          <t>547988</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13288</t>
+          <t>12256</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17760</t>
+          <t>17321</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>601739</t>
+          <t>602771</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>613254</t>
+          <t>613169</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>628625</t>
+          <t>628630</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>637248</t>
+          <t>637247</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1235486</t>
+          <t>1235925</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1248529</t>
+          <t>1248704</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27834</t>
+          <t>28652</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13613</t>
+          <t>12902</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33269</t>
+          <t>32607</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28923</t>
+          <t>28907</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>55248</t>
+          <t>54971</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>715961</t>
+          <t>715143</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>731653</t>
+          <t>732050</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>750242</t>
+          <t>750904</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>769898</t>
+          <t>770609</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1472058</t>
+          <t>1472335</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1498383</t>
+          <t>1498399</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26480</t>
+          <t>26081</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49392</t>
+          <t>49788</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>37609</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>68044</t>
+          <t>66395</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>68992</t>
+          <t>68472</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>106354</t>
+          <t>106966</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3227151</t>
+          <t>3226755</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3250063</t>
+          <t>3250462</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3311153</t>
+          <t>3312802</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3340889</t>
+          <t>3341588</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6549387</t>
+          <t>6548775</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6586749</t>
+          <t>6587269</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>8167</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>928</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8729</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>279392</t>
+          <t>279078</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286312</t>
+          <t>286313</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573254</t>
+          <t>574056</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>581051</t>
+          <t>581055</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23199</t>
+          <t>24171</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24628</t>
+          <t>24518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>499816</t>
+          <t>500203</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>499457</t>
+          <t>498485</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>515992</t>
+          <t>516124</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1003556</t>
+          <t>1003666</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1020335</t>
+          <t>1020421</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>334538</t>
+          <t>334526</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>657766</t>
+          <t>657670</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15528</t>
+          <t>16754</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>367085</t>
+          <t>367478</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>376418</t>
+          <t>376606</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386717</t>
+          <t>386146</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>747405</t>
+          <t>746179</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>759006</t>
+          <t>758906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14041</t>
+          <t>13400</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19203</t>
+          <t>18952</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8389</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27672</t>
+          <t>26176</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198577</t>
+          <t>199218</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211580</t>
+          <t>211571</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200388</t>
+          <t>200639</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214267</t>
+          <t>214365</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>404537</t>
+          <t>406033</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>423820</t>
+          <t>423810</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>11286</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12596</t>
+          <t>12410</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>269169</t>
+          <t>268445</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>266517</t>
+          <t>266810</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276040</t>
+          <t>275994</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>539481</t>
+          <t>539667</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549965</t>
+          <t>549973</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>5832</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19183</t>
+          <t>20206</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>16491</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11873</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30842</t>
+          <t>30201</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>643605</t>
+          <t>642582</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>657666</t>
+          <t>656956</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>677551</t>
+          <t>677362</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>689944</t>
+          <t>690081</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1325799</t>
+          <t>1326440</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1344768</t>
+          <t>1345912</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9282</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18537</t>
+          <t>18806</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21735</t>
+          <t>21752</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>769816</t>
+          <t>770790</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>778081</t>
+          <t>778078</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>804041</t>
+          <t>803772</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>818187</t>
+          <t>818038</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1579941</t>
+          <t>1579924</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1595070</t>
+          <t>1594338</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13565</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>34740</t>
+          <t>35835</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>43029</t>
+          <t>43559</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>75272</t>
+          <t>73835</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>64090</t>
+          <t>62191</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>101372</t>
+          <t>100231</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3392039</t>
+          <t>3390944</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3413214</t>
+          <t>3412516</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3478718</t>
+          <t>3480155</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3510961</t>
+          <t>3510431</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6879397</t>
+          <t>6880538</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6916679</t>
+          <t>6918578</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>782</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11362</t>
+          <t>13047</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16181</t>
+          <t>15945</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284985</t>
+          <t>286352</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292962</t>
+          <t>292979</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>277341</t>
+          <t>275656</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286816</t>
+          <t>286669</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>566283</t>
+          <t>566519</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578547</t>
+          <t>578553</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>861</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11204</t>
+          <t>11572</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3371</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15960</t>
+          <t>14822</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>495485</t>
+          <t>495563</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501716</t>
+          <t>501714</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>511880</t>
+          <t>511512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>521920</t>
+          <t>521911</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1009699</t>
+          <t>1010837</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1022249</t>
+          <t>1022288</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24356</t>
+          <t>26236</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,47 +8457,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>16142</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>8981</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>27189</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>2,13%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>16142</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>9522</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>26170</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>365076</t>
+          <t>365087</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>362927</t>
+          <t>361047</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>379038</t>
+          <t>378993</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,47 +8570,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>741105</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>730058</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>748266</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>97,87%</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>741105</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>731077</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>747725</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>97,87%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>206405</t>
+          <t>205563</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>425032</t>
+          <t>425019</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>10142</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>958</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15258</t>
+          <t>15076</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253614</t>
+          <t>252981</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261512</t>
+          <t>261477</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>263900</t>
+          <t>263855</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272156</t>
+          <t>272157</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>520980</t>
+          <t>521162</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532582</t>
+          <t>532733</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>910</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9456,42 +9456,42 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>16478</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>9550</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>27007</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>16478</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>9371</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>26552</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12001</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31320</t>
+          <t>31470</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>647519</t>
+          <t>647574</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>655651</t>
+          <t>655648</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,49 +9564,49 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>98,63%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>674816</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>664287</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>681744</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>97,62%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>96,09%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
           <t>98,62%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,86%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>674816</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>664742</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>681923</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>97,62%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>96,16%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1208</t>
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1316532</t>
+          <t>1316382</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1335851</t>
+          <t>1335330</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>8858</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12749</t>
+          <t>12879</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16849</t>
+          <t>16729</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>770390</t>
+          <t>769725</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>813418</t>
+          <t>813288</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>824024</t>
+          <t>824108</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1587901</t>
+          <t>1588021</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1601403</t>
+          <t>1601289</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26279</t>
+          <t>27785</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38462</t>
+          <t>35140</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>69353</t>
+          <t>67268</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>53794</t>
+          <t>54011</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>87626</t>
+          <t>88710</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3368071</t>
+          <t>3366565</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3383759</t>
+          <t>3383873</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3475189</t>
+          <t>3477274</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3506080</t>
+          <t>3509402</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6851266</t>
+          <t>6850182</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6885098</t>
+          <t>6884881</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
